--- a/subir/jugadores.xlsx
+++ b/subir/jugadores.xlsx
@@ -5,14 +5,15 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\appflutter\handball_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\appflutter\handball_app\subir\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Cadetes" sheetId="1" r:id="rId1"/>
+    <sheet name="Juveniles" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,84 +25,225 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="73">
   <si>
     <t>Nro camiseta</t>
   </si>
   <si>
-    <t>Nombre jugador</t>
-  </si>
-  <si>
-    <t>Bautista Galante Saavedra</t>
-  </si>
-  <si>
     <t>Posicion</t>
   </si>
   <si>
     <t>Arquero</t>
   </si>
   <si>
-    <t>Juan Frascarelli</t>
-  </si>
-  <si>
     <t>Pivot</t>
   </si>
   <si>
-    <t>Julian Della Vecchia</t>
-  </si>
-  <si>
     <t>Central</t>
   </si>
   <si>
     <t>Extremo izquierdo</t>
   </si>
   <si>
-    <t>Joaquin Leon Rodriguez</t>
-  </si>
-  <si>
-    <t>Juan Pundang</t>
-  </si>
-  <si>
     <t>Lateral derecho</t>
   </si>
   <si>
     <t>Extremo derecho</t>
   </si>
   <si>
-    <t>Agustin Del Groso</t>
-  </si>
-  <si>
     <t>Lateral izquierdo</t>
   </si>
   <si>
-    <t>Guibando</t>
-  </si>
-  <si>
-    <t>Francisco Parente</t>
-  </si>
-  <si>
-    <t>Lautaro Zapata</t>
-  </si>
-  <si>
-    <t>Lorenzo Guiñazu</t>
-  </si>
-  <si>
-    <t>Ulises Lopez Aranda</t>
-  </si>
-  <si>
     <t>extremo izquierdo</t>
   </si>
   <si>
-    <t>Lucas Fontana Bondar</t>
-  </si>
-  <si>
-    <t>Bautista Villarino</t>
-  </si>
-  <si>
-    <t>Felipe Palacios</t>
-  </si>
-  <si>
-    <t>Facundo Avero</t>
+    <t>categoria</t>
+  </si>
+  <si>
+    <t>Cadetes</t>
+  </si>
+  <si>
+    <t>Lorenzo</t>
+  </si>
+  <si>
+    <t>Luciano</t>
+  </si>
+  <si>
+    <t>Valentin</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>Bautista</t>
+  </si>
+  <si>
+    <t>Agustin</t>
+  </si>
+  <si>
+    <t>Tiziano</t>
+  </si>
+  <si>
+    <t>Felipe</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Joaquin</t>
+  </si>
+  <si>
+    <t>Benicio</t>
+  </si>
+  <si>
+    <t>Alejo</t>
+  </si>
+  <si>
+    <t>Federico</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Galante Saavedra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Frascarelli</t>
+  </si>
+  <si>
+    <t>Julian</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Della Vecchia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Leon Rodriguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pundang</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Parente</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fontana Bondar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Villarino</t>
+  </si>
+  <si>
+    <t>Ulises</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lopez Aranda</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Palacios</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Del Groso</t>
+  </si>
+  <si>
+    <t>Facundo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Avero</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Guiñazu</t>
+  </si>
+  <si>
+    <t>Lautaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Zapata</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Farias</t>
+  </si>
+  <si>
+    <t>Baron Siccardi</t>
+  </si>
+  <si>
+    <t>Farfallini</t>
+  </si>
+  <si>
+    <t>Villar Senra</t>
+  </si>
+  <si>
+    <t>Medan</t>
+  </si>
+  <si>
+    <t>Sanches</t>
+  </si>
+  <si>
+    <t>Salgado</t>
+  </si>
+  <si>
+    <t>Dominguez Bianco</t>
+  </si>
+  <si>
+    <t>Drewanz</t>
+  </si>
+  <si>
+    <t>Folino Carames</t>
+  </si>
+  <si>
+    <t>Verdejo</t>
+  </si>
+  <si>
+    <t>Riesgo Santos</t>
+  </si>
+  <si>
+    <t>Alcaraz</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t>Dominguez Rividdi</t>
+  </si>
+  <si>
+    <t>Fernandez</t>
+  </si>
+  <si>
+    <t>Ricalde</t>
+  </si>
+  <si>
+    <t>Pundang</t>
+  </si>
+  <si>
+    <t>Juan Manuel</t>
+  </si>
+  <si>
+    <t>Francisco Javier</t>
+  </si>
+  <si>
+    <t>Mario Bautista</t>
+  </si>
+  <si>
+    <t>Agustin Emanuel</t>
+  </si>
+  <si>
+    <t>Alvaro Joaquin</t>
+  </si>
+  <si>
+    <t>Jairo Uriel</t>
+  </si>
+  <si>
+    <t>Juveniles</t>
   </si>
 </sst>
 </file>
@@ -137,8 +279,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,174 +564,562 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>33</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
